--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118438061</v>
+        <v>118438128</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,10 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R2" t="n">
-        <v>6567837</v>
+        <v>6567828</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,11 +779,6 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tre blommande knärot. Flera plantor i mossan.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -797,7 +796,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -815,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118428803</v>
+        <v>118438511</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -848,11 +847,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -871,10 +866,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569708</v>
+        <v>569706</v>
       </c>
       <c r="R3" t="n">
-        <v>6567665</v>
+        <v>6567855</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -906,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +911,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Blommande knärot i sluttning ner mot Hjälmaren. Kalkrik morän.</t>
+          <t>Flertalet blommande knärot och fler plantor i mossan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,7 +936,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118438128</v>
+        <v>118429258</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>100017</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,40 +966,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1015,13 +1002,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569706</v>
+        <v>569704</v>
       </c>
       <c r="R4" t="n">
-        <v>6567828</v>
+        <v>6567630</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1050,7 +1037,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1060,7 +1047,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,7 +1072,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog på kalkrik morän</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1098,7 +1090,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118428861</v>
+        <v>118428803</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1133,7 +1125,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1141,7 +1133,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1150,10 +1146,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569660</v>
+        <v>569708</v>
       </c>
       <c r="R5" t="n">
-        <v>6567633</v>
+        <v>6567665</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1200,7 +1196,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En blommande knärot i beståndet. Kalkrik morän.</t>
+          <t>Blommande knärot i sluttning ner mot Hjälmaren. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1238,10 +1234,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118429258</v>
+        <v>118428969</v>
       </c>
       <c r="B6" t="n">
-        <v>100017</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1250,34 +1246,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569704</v>
+        <v>569666</v>
       </c>
       <c r="R6" t="n">
-        <v>6567630</v>
+        <v>6567639</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
+          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118438511</v>
+        <v>118429021</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1407,17 +1407,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569706</v>
+        <v>569675</v>
       </c>
       <c r="R7" t="n">
-        <v>6567855</v>
+        <v>6567631</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet blommande knärot och fler plantor i mossan</t>
+          <t>Växer i välutvecklade mossmattor i äldre barrskog som sluttar mot Hjälmaren. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1514,7 +1514,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118429021</v>
+        <v>118428861</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569675</v>
+        <v>569660</v>
       </c>
       <c r="R8" t="n">
-        <v>6567631</v>
+        <v>6567633</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer i välutvecklade mossmattor i äldre barrskog som sluttar mot Hjälmaren. Kalkrik morän.</t>
+          <t>En blommande knärot i beståndet. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118428969</v>
+        <v>118438061</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1689,15 +1689,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569666</v>
+        <v>569696</v>
       </c>
       <c r="R9" t="n">
-        <v>6567639</v>
+        <v>6567837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
+          <t>Tre blommande knärot. Flera plantor i mossan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118520916</v>
+        <v>118520903</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1971,11 +1971,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -1990,13 +1986,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569695</v>
+        <v>569744</v>
       </c>
       <c r="R11" t="n">
-        <v>6567585</v>
+        <v>6567744</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2025,7 +2021,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2035,12 +2031,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera blommande k närot och plantor i mossan.</t>
+          <t>Blommande knärot. Flera plantor.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2078,7 +2074,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118520959</v>
+        <v>118521013</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2111,17 +2107,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2130,13 +2126,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569721</v>
+        <v>569749</v>
       </c>
       <c r="R12" t="n">
-        <v>6567579</v>
+        <v>6567617</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2180,7 +2176,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
+          <t>Blommande knärot och flertalet plantor, rosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2218,7 +2214,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118520903</v>
+        <v>118520893</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2266,10 +2262,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569744</v>
+        <v>569758</v>
       </c>
       <c r="R13" t="n">
-        <v>6567744</v>
+        <v>6567702</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2299,24 +2295,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Blommande knärot. Flera plantor.</t>
+          <t>Blommande knärot i sluttning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2354,7 +2340,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118520893</v>
+        <v>118520916</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2387,7 +2373,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -2402,13 +2392,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569758</v>
+        <v>569695</v>
       </c>
       <c r="R14" t="n">
-        <v>6567702</v>
+        <v>6567585</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2435,14 +2425,24 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blommande knärot i sluttning.</t>
+          <t>Flera blommande k närot och plantor i mossan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118521013</v>
+        <v>118520959</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2513,17 +2513,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2532,13 +2532,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569749</v>
+        <v>569721</v>
       </c>
       <c r="R15" t="n">
-        <v>6567617</v>
+        <v>6567579</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Blommande knärot och flertalet plantor, rosetter</t>
+          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118438128</v>
+        <v>118438511</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -708,11 +708,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -734,10 +730,10 @@
         <v>569706</v>
       </c>
       <c r="R2" t="n">
-        <v>6567828</v>
+        <v>6567855</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,6 +773,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet blommande knärot och fler plantor i mossan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +797,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +815,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118438511</v>
+        <v>118428861</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -847,17 +848,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -866,10 +867,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569706</v>
+        <v>569660</v>
       </c>
       <c r="R3" t="n">
-        <v>6567855</v>
+        <v>6567633</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,12 +912,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flertalet blommande knärot och fler plantor i mossan</t>
+          <t>En blommande knärot i beståndet. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +937,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118429258</v>
+        <v>118428969</v>
       </c>
       <c r="B4" t="n">
-        <v>100017</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,34 +967,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1002,13 +1007,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569704</v>
+        <v>569666</v>
       </c>
       <c r="R4" t="n">
-        <v>6567630</v>
+        <v>6567639</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1052,7 +1057,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
+          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,7 +1077,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1234,7 +1239,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118428969</v>
+        <v>118438061</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1269,15 +1274,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1286,10 +1291,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569666</v>
+        <v>569696</v>
       </c>
       <c r="R6" t="n">
-        <v>6567639</v>
+        <v>6567837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1321,7 +1326,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1331,12 +1336,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
+          <t>Tre blommande knärot. Flera plantor i mossan.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,7 +1361,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1374,10 +1379,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118429021</v>
+        <v>118429258</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>100017</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,38 +1391,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1426,10 +1427,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569675</v>
+        <v>569704</v>
       </c>
       <c r="R7" t="n">
-        <v>6567631</v>
+        <v>6567630</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1476,7 +1477,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer i välutvecklade mossmattor i äldre barrskog som sluttar mot Hjälmaren. Kalkrik morän.</t>
+          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1496,7 +1497,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän.</t>
+          <t>Äldre barrskog på kalkrik morän</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1514,7 +1515,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118428861</v>
+        <v>118429021</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1549,7 +1550,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569660</v>
+        <v>569675</v>
       </c>
       <c r="R8" t="n">
-        <v>6567633</v>
+        <v>6567631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1616,7 +1617,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En blommande knärot i beståndet. Kalkrik morän.</t>
+          <t>Växer i välutvecklade mossmattor i äldre barrskog som sluttar mot Hjälmaren. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,7 +1637,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1654,7 +1655,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118438061</v>
+        <v>118438128</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1689,10 +1690,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1706,10 +1711,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R9" t="n">
-        <v>6567837</v>
+        <v>6567828</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1754,11 +1759,6 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tre blommande knärot. Flera plantor i mossan.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118520975</v>
+        <v>118520916</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1829,14 +1829,10 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1850,13 +1846,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569735</v>
+        <v>569695</v>
       </c>
       <c r="R10" t="n">
-        <v>6567574</v>
+        <v>6567585</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1900,7 +1896,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Blommande knärot och många rosetter i mossan.</t>
+          <t>Flera blommande k närot och plantor i mossan.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1938,7 +1934,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118520903</v>
+        <v>118520975</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1971,8 +1967,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1986,10 +1990,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569744</v>
+        <v>569735</v>
       </c>
       <c r="R11" t="n">
-        <v>6567744</v>
+        <v>6567574</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2021,7 +2025,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2031,12 +2035,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Blommande knärot. Flera plantor.</t>
+          <t>Blommande knärot och många rosetter i mossan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2074,7 +2078,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118521013</v>
+        <v>118520893</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -2108,11 +2112,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569749</v>
+        <v>569758</v>
       </c>
       <c r="R12" t="n">
-        <v>6567617</v>
+        <v>6567702</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2159,24 +2159,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Blommande knärot och flertalet plantor, rosetter</t>
+          <t>Blommande knärot i sluttning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2214,7 +2204,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118520893</v>
+        <v>118520903</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2262,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569758</v>
+        <v>569744</v>
       </c>
       <c r="R13" t="n">
-        <v>6567702</v>
+        <v>6567744</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2295,14 +2285,24 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Blommande knärot i sluttning.</t>
+          <t>Blommande knärot. Flera plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2340,7 +2340,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118520916</v>
+        <v>118520959</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2375,15 +2375,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569695</v>
+        <v>569721</v>
       </c>
       <c r="R14" t="n">
-        <v>6567585</v>
+        <v>6567579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera blommande k närot och plantor i mossan.</t>
+          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2480,7 +2480,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118520959</v>
+        <v>118521013</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2513,17 +2513,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2532,13 +2532,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569721</v>
+        <v>569749</v>
       </c>
       <c r="R15" t="n">
-        <v>6567579</v>
+        <v>6567617</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
+          <t>Blommande knärot och flertalet plantor, rosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118438511</v>
+        <v>118438128</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,7 +708,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -730,10 +734,10 @@
         <v>569706</v>
       </c>
       <c r="R2" t="n">
-        <v>6567855</v>
+        <v>6567828</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,11 +777,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>18:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet blommande knärot och fler plantor i mossan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +796,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -818,7 +817,7 @@
         <v>118428861</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -955,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118428969</v>
+        <v>118438061</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -990,15 +989,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1007,10 +1006,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569666</v>
+        <v>569696</v>
       </c>
       <c r="R4" t="n">
-        <v>6567639</v>
+        <v>6567837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1042,7 +1041,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1052,12 +1051,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
+          <t>Tre blommande knärot. Flera plantor i mossan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,7 +1076,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1095,10 +1094,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118428803</v>
+        <v>118429258</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>100024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1107,40 +1106,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1151,10 +1142,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569708</v>
+        <v>569704</v>
       </c>
       <c r="R5" t="n">
-        <v>6567665</v>
+        <v>6567630</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1201,7 +1192,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Blommande knärot i sluttning ner mot Hjälmaren. Kalkrik morän.</t>
+          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1221,7 +1212,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog på kalkrik morän</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1239,10 +1230,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118438061</v>
+        <v>118438511</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1272,12 +1263,12 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1291,13 +1282,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569696</v>
+        <v>569706</v>
       </c>
       <c r="R6" t="n">
-        <v>6567837</v>
+        <v>6567855</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1341,7 +1332,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tre blommande knärot. Flera plantor i mossan.</t>
+          <t>Flertalet blommande knärot och fler plantor i mossan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1361,7 +1352,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1379,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118429258</v>
+        <v>118428969</v>
       </c>
       <c r="B7" t="n">
-        <v>100017</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,34 +1382,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1427,13 +1422,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569704</v>
+        <v>569666</v>
       </c>
       <c r="R7" t="n">
-        <v>6567630</v>
+        <v>6567639</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1477,7 +1472,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
+          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1497,7 +1492,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1518,7 +1513,7 @@
         <v>118429021</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1655,10 +1650,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118438128</v>
+        <v>118428803</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1711,13 +1706,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569706</v>
+        <v>569708</v>
       </c>
       <c r="R9" t="n">
-        <v>6567828</v>
+        <v>6567665</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1746,7 +1741,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1756,7 +1751,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Blommande knärot i sluttning ner mot Hjälmaren. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1797,7 +1797,7 @@
         <v>118520916</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118520975</v>
+        <v>118520959</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1977,11 +1977,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1990,13 +1986,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569735</v>
+        <v>569721</v>
       </c>
       <c r="R11" t="n">
-        <v>6567574</v>
+        <v>6567579</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2040,7 +2036,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Blommande knärot och många rosetter i mossan.</t>
+          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2078,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118520893</v>
+        <v>118521013</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2112,7 +2108,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569758</v>
+        <v>569749</v>
       </c>
       <c r="R12" t="n">
-        <v>6567702</v>
+        <v>6567617</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2159,14 +2159,24 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Blommande knärot i sluttning.</t>
+          <t>Blommande knärot och flertalet plantor, rosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2204,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118520903</v>
+        <v>118520975</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2237,8 +2247,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2252,10 +2270,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569744</v>
+        <v>569735</v>
       </c>
       <c r="R13" t="n">
-        <v>6567744</v>
+        <v>6567574</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2287,7 +2305,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2297,12 +2315,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Blommande knärot. Flera plantor.</t>
+          <t>Blommande knärot och många rosetter i mossan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2340,10 +2358,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118520959</v>
+        <v>118520893</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2373,17 +2391,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2392,13 +2406,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569721</v>
+        <v>569758</v>
       </c>
       <c r="R14" t="n">
-        <v>6567579</v>
+        <v>6567702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2425,24 +2439,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
+          <t>Blommande knärot i sluttning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2480,10 +2484,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118521013</v>
+        <v>118520903</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2514,11 +2518,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569749</v>
+        <v>569744</v>
       </c>
       <c r="R15" t="n">
-        <v>6567617</v>
+        <v>6567744</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Blommande knärot och flertalet plantor, rosetter</t>
+          <t>Blommande knärot. Flera plantor.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118438128</v>
+        <v>118428861</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,11 +718,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569706</v>
+        <v>569660</v>
       </c>
       <c r="R2" t="n">
-        <v>6567828</v>
+        <v>6567633</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En blommande knärot i beståndet. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -814,7 +815,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118428861</v>
+        <v>118438061</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -849,15 +850,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -866,13 +867,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569660</v>
+        <v>569696</v>
       </c>
       <c r="R3" t="n">
-        <v>6567633</v>
+        <v>6567837</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,12 +912,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En blommande knärot i beståndet. Kalkrik morän.</t>
+          <t>Tre blommande knärot. Flera plantor i mossan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +937,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,7 +955,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118438061</v>
+        <v>118428969</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -989,15 +990,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1006,10 +1007,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569696</v>
+        <v>569666</v>
       </c>
       <c r="R4" t="n">
-        <v>6567837</v>
+        <v>6567639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1051,12 +1052,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tre blommande knärot. Flera plantor i mossan.</t>
+          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1076,7 +1077,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1094,10 +1095,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118429258</v>
+        <v>118429021</v>
       </c>
       <c r="B5" t="n">
-        <v>100024</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,34 +1107,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569704</v>
+        <v>569675</v>
       </c>
       <c r="R5" t="n">
-        <v>6567630</v>
+        <v>6567631</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
+          <t>Växer i välutvecklade mossmattor i äldre barrskog som sluttar mot Hjälmaren. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,7 +1217,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän</t>
+          <t>Äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118428969</v>
+        <v>118429258</v>
       </c>
       <c r="B7" t="n">
-        <v>97853</v>
+        <v>100024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,38 +1387,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1422,13 +1423,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569666</v>
+        <v>569704</v>
       </c>
       <c r="R7" t="n">
-        <v>6567639</v>
+        <v>6567630</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1472,7 +1473,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer i fin gammal barrskog med äldre mossmattor. Kalkrik morän.</t>
+          <t>Fint bestånd av svart trolldruva i äldre barrskog på kalkrik morän.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1492,7 +1493,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrskog</t>
+          <t>Äldre barrskog på kalkrik morän</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1510,7 +1511,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118429021</v>
+        <v>118428803</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1545,7 +1546,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1553,7 +1554,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569675</v>
+        <v>569708</v>
       </c>
       <c r="R8" t="n">
-        <v>6567631</v>
+        <v>6567665</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1612,7 +1617,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer i välutvecklade mossmattor i äldre barrskog som sluttar mot Hjälmaren. Kalkrik morän.</t>
+          <t>Blommande knärot i sluttning ner mot Hjälmaren. Kalkrik morän.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1632,7 +1637,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog på kalkrik morän.</t>
+          <t>Äldre barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1650,7 +1655,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118428803</v>
+        <v>118438128</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1685,7 +1690,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1706,13 +1711,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569708</v>
+        <v>569706</v>
       </c>
       <c r="R9" t="n">
-        <v>6567665</v>
+        <v>6567828</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1741,7 +1746,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1751,12 +1756,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Blommande knärot i sluttning ner mot Hjälmaren. Kalkrik morän.</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1794,7 +1794,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118520916</v>
+        <v>118520893</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1827,11 +1827,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -1846,13 +1842,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569695</v>
+        <v>569758</v>
       </c>
       <c r="R10" t="n">
-        <v>6567585</v>
+        <v>6567702</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1879,24 +1875,14 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera blommande k närot och plantor i mossan.</t>
+          <t>Blommande knärot i sluttning.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1934,7 +1920,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118520959</v>
+        <v>118520916</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1969,15 +1955,15 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1986,10 +1972,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569721</v>
+        <v>569695</v>
       </c>
       <c r="R11" t="n">
-        <v>6567579</v>
+        <v>6567585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2036,7 +2022,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
+          <t>Flera blommande k närot och plantor i mossan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2074,7 +2060,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118521013</v>
+        <v>118520959</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -2107,17 +2093,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2126,13 +2112,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569749</v>
+        <v>569721</v>
       </c>
       <c r="R12" t="n">
-        <v>6567617</v>
+        <v>6567579</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2176,7 +2162,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Blommande knärot och flertalet plantor, rosetter</t>
+          <t>Blommande knärot och ett trettiotal plantor, förmodligen fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2214,7 +2200,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118520975</v>
+        <v>118521013</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -2247,11 +2233,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2270,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569735</v>
+        <v>569749</v>
       </c>
       <c r="R13" t="n">
-        <v>6567574</v>
+        <v>6567617</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2320,7 +2302,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Blommande knärot och många rosetter i mossan.</t>
+          <t>Blommande knärot och flertalet plantor, rosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2358,7 +2340,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118520893</v>
+        <v>118520975</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2391,8 +2373,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2406,10 +2396,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569758</v>
+        <v>569735</v>
       </c>
       <c r="R14" t="n">
-        <v>6567702</v>
+        <v>6567574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2439,14 +2429,24 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blommande knärot i sluttning.</t>
+          <t>Blommande knärot och många rosetter i mossan.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2618,6 +2618,769 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120262576</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Barråsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>569749</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6567499</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor inom 4 kvm.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120263531</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Granhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>569680</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6567608</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120262815</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Barråsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>569754</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6567498</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120263624</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>569709</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6567641</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120263041</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Barråsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>569784</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6567476</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120265400</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Barråsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>569774</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6567496</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120262576</v>
+        <v>120263624</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2668,14 +2668,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569749</v>
+        <v>569709</v>
       </c>
       <c r="R16" t="n">
-        <v>6567499</v>
+        <v>6567641</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2717,12 +2717,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 100 plantor inom 4 kvm.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2749,10 +2744,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120263531</v>
+        <v>120265400</v>
       </c>
       <c r="B17" t="n">
-        <v>57679</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2761,25 +2756,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2795,23 +2790,23 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569680</v>
+        <v>569774</v>
       </c>
       <c r="R17" t="n">
-        <v>6567608</v>
+        <v>6567496</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2840,7 +2835,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2850,7 +2845,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2877,10 +2872,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120262815</v>
+        <v>120262576</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2912,7 +2907,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2929,13 +2924,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569754</v>
+        <v>569749</v>
       </c>
       <c r="R18" t="n">
-        <v>6567498</v>
+        <v>6567499</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2964,7 +2959,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2974,12 +2969,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>Ca 100 plantor inom 4 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3006,10 +3001,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120263624</v>
+        <v>120263041</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3041,30 +3036,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569709</v>
+        <v>569784</v>
       </c>
       <c r="R19" t="n">
-        <v>6567641</v>
+        <v>6567476</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3093,7 +3084,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3103,7 +3094,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3126,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120263041</v>
+        <v>120263531</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>57689</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3142,49 +3138,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569784</v>
+        <v>569680</v>
       </c>
       <c r="R20" t="n">
-        <v>6567476</v>
+        <v>6567608</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3223,12 +3227,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3255,10 +3254,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120265400</v>
+        <v>120262815</v>
       </c>
       <c r="B21" t="n">
-        <v>57463</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3267,43 +3266,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3311,10 +3306,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569774</v>
+        <v>569754</v>
       </c>
       <c r="R21" t="n">
-        <v>6567496</v>
+        <v>6567498</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3356,7 +3351,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -2744,10 +2744,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120265400</v>
+        <v>120262815</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2756,43 +2756,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2800,10 +2796,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569774</v>
+        <v>569754</v>
       </c>
       <c r="R17" t="n">
-        <v>6567496</v>
+        <v>6567498</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2835,7 +2831,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2845,7 +2841,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3001,10 +3002,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120263041</v>
+        <v>120265400</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3013,35 +3014,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3049,13 +3058,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569784</v>
+        <v>569774</v>
       </c>
       <c r="R19" t="n">
-        <v>6567476</v>
+        <v>6567496</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3084,7 +3093,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3094,12 +3103,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3126,10 +3130,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120263531</v>
+        <v>120263041</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3138,57 +3142,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569680</v>
+        <v>569784</v>
       </c>
       <c r="R20" t="n">
-        <v>6567608</v>
+        <v>6567476</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3227,7 +3223,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3254,10 +3255,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120262815</v>
+        <v>120263531</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3266,53 +3267,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569754</v>
+        <v>569680</v>
       </c>
       <c r="R21" t="n">
-        <v>6567498</v>
+        <v>6567608</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3351,12 +3356,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120263624</v>
+        <v>120263531</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2632,39 +2632,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2672,13 +2676,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569709</v>
+        <v>569680</v>
       </c>
       <c r="R16" t="n">
-        <v>6567641</v>
+        <v>6567608</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2707,7 +2711,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2717,7 +2721,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2744,7 +2748,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120262815</v>
+        <v>120263624</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2779,7 +2783,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2792,17 +2796,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569754</v>
+        <v>569709</v>
       </c>
       <c r="R17" t="n">
-        <v>6567498</v>
+        <v>6567641</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2841,12 +2845,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2873,7 +2872,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120262576</v>
+        <v>120262815</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2908,7 +2907,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2925,13 +2924,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569749</v>
+        <v>569754</v>
       </c>
       <c r="R18" t="n">
-        <v>6567499</v>
+        <v>6567498</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2960,7 +2959,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2970,12 +2969,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 100 plantor inom 4 kvm.</t>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3002,10 +3001,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120265400</v>
+        <v>120262576</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3014,43 +3013,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3058,13 +3053,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569774</v>
+        <v>569749</v>
       </c>
       <c r="R19" t="n">
-        <v>6567496</v>
+        <v>6567499</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3093,7 +3088,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3103,7 +3098,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor inom 4 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120263041</v>
+        <v>120265400</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3142,35 +3142,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3178,13 +3186,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569784</v>
+        <v>569774</v>
       </c>
       <c r="R20" t="n">
-        <v>6567476</v>
+        <v>6567496</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3213,7 +3221,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3223,12 +3231,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3255,10 +3258,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120263531</v>
+        <v>120263041</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3267,57 +3270,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569680</v>
+        <v>569784</v>
       </c>
       <c r="R21" t="n">
-        <v>6567608</v>
+        <v>6567476</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3356,7 +3351,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120263531</v>
+        <v>120263624</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2632,43 +2632,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2676,13 +2672,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569680</v>
+        <v>569709</v>
       </c>
       <c r="R16" t="n">
-        <v>6567608</v>
+        <v>6567641</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2711,7 +2707,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2721,7 +2717,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2748,10 +2744,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120263624</v>
+        <v>120265400</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2760,53 +2756,57 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569709</v>
+        <v>569774</v>
       </c>
       <c r="R17" t="n">
-        <v>6567641</v>
+        <v>6567496</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2872,7 +2872,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120262815</v>
+        <v>120263041</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2907,14 +2907,10 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2924,13 +2920,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569754</v>
+        <v>569784</v>
       </c>
       <c r="R18" t="n">
-        <v>6567498</v>
+        <v>6567476</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2959,7 +2955,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2969,12 +2965,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3001,10 +2997,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120262576</v>
+        <v>120263531</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3013,53 +3009,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569749</v>
+        <v>569680</v>
       </c>
       <c r="R19" t="n">
-        <v>6567499</v>
+        <v>6567608</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3098,12 +3098,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ca 100 plantor inom 4 kvm.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3125,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120265400</v>
+        <v>120262576</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3142,43 +3137,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3186,13 +3177,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569774</v>
+        <v>569749</v>
       </c>
       <c r="R20" t="n">
-        <v>6567496</v>
+        <v>6567499</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3221,7 +3212,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3231,7 +3222,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor inom 4 kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3258,7 +3254,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120263041</v>
+        <v>120262815</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3293,10 +3289,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569784</v>
+        <v>569754</v>
       </c>
       <c r="R21" t="n">
-        <v>6567476</v>
+        <v>6567498</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120263624</v>
+        <v>120263531</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2632,39 +2632,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2672,13 +2676,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569709</v>
+        <v>569680</v>
       </c>
       <c r="R16" t="n">
-        <v>6567641</v>
+        <v>6567608</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2707,7 +2711,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2717,7 +2721,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2744,10 +2748,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120265400</v>
+        <v>120263041</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2756,43 +2760,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2800,13 +2796,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569774</v>
+        <v>569784</v>
       </c>
       <c r="R17" t="n">
-        <v>6567496</v>
+        <v>6567476</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2835,7 +2831,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2845,7 +2841,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2872,7 +2873,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120263041</v>
+        <v>120262815</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2907,10 +2908,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2920,13 +2925,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569784</v>
+        <v>569754</v>
       </c>
       <c r="R18" t="n">
-        <v>6567476</v>
+        <v>6567498</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2955,7 +2960,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2965,12 +2970,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2997,10 +3002,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120263531</v>
+        <v>120262576</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3009,57 +3014,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569680</v>
+        <v>569749</v>
       </c>
       <c r="R19" t="n">
-        <v>6567608</v>
+        <v>6567499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3088,7 +3089,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3098,7 +3099,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor inom 4 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3125,10 +3131,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120262576</v>
+        <v>120265400</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3137,39 +3143,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3177,13 +3187,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569749</v>
+        <v>569774</v>
       </c>
       <c r="R20" t="n">
-        <v>6567499</v>
+        <v>6567496</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3212,7 +3222,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3222,12 +3232,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 100 plantor inom 4 kvm.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3254,7 +3259,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120262815</v>
+        <v>120263624</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3289,7 +3294,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3302,17 +3307,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569754</v>
+        <v>569709</v>
       </c>
       <c r="R21" t="n">
-        <v>6567498</v>
+        <v>6567641</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3341,7 +3346,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3351,12 +3356,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -2620,10 +2620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120263531</v>
+        <v>120262576</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2632,57 +2632,53 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569680</v>
+        <v>569749</v>
       </c>
       <c r="R16" t="n">
-        <v>6567608</v>
+        <v>6567499</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2711,7 +2707,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2721,7 +2717,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor inom 4 kvm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2748,10 +2749,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120263041</v>
+        <v>120265400</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2760,35 +2761,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2796,13 +2805,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569784</v>
+        <v>569774</v>
       </c>
       <c r="R17" t="n">
-        <v>6567476</v>
+        <v>6567496</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2831,7 +2840,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2841,12 +2850,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2873,7 +2877,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120262815</v>
+        <v>120263041</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2908,14 +2912,10 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2925,13 +2925,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569754</v>
+        <v>569784</v>
       </c>
       <c r="R18" t="n">
-        <v>6567498</v>
+        <v>6567476</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3002,10 +3002,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120262576</v>
+        <v>120263531</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3014,53 +3014,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569749</v>
+        <v>569680</v>
       </c>
       <c r="R19" t="n">
-        <v>6567499</v>
+        <v>6567608</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3089,7 +3093,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3099,12 +3103,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ca 100 plantor inom 4 kvm.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3131,10 +3130,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120265400</v>
+        <v>120262815</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3143,43 +3142,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3187,10 +3182,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569774</v>
+        <v>569754</v>
       </c>
       <c r="R20" t="n">
-        <v>6567496</v>
+        <v>6567498</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -3222,7 +3217,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3232,7 +3227,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120262576</v>
+        <v>120262815</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569749</v>
+        <v>569754</v>
       </c>
       <c r="R16" t="n">
-        <v>6567499</v>
+        <v>6567498</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ca 100 plantor inom 4 kvm.</t>
+          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2877,7 +2877,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120263041</v>
+        <v>120263624</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2912,26 +2912,30 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569784</v>
+        <v>569709</v>
       </c>
       <c r="R18" t="n">
-        <v>6567476</v>
+        <v>6567641</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2960,7 +2964,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2970,12 +2974,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3002,10 +3001,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120263531</v>
+        <v>120262576</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3014,57 +3013,53 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569680</v>
+        <v>569749</v>
       </c>
       <c r="R19" t="n">
-        <v>6567608</v>
+        <v>6567499</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3093,7 +3088,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3103,7 +3098,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor inom 4 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120262815</v>
+        <v>120263531</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57689</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3142,53 +3142,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barråsen, Srm</t>
+          <t>Granhult, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569754</v>
+        <v>569680</v>
       </c>
       <c r="R20" t="n">
-        <v>6567498</v>
+        <v>6567608</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3217,7 +3221,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3227,12 +3231,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 40 plantor i mossan inom område av 3 kvm</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3259,7 +3258,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120263624</v>
+        <v>120263041</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3294,30 +3293,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Granhult, Srm</t>
+          <t>Barråsen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569709</v>
+        <v>569784</v>
       </c>
       <c r="R21" t="n">
-        <v>6567641</v>
+        <v>6567476</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3356,7 +3351,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor i mossan. Inom område av 4 kvm</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3380,6 +3380,255 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120551191</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Granhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>569705</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6567616</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Räknade till elva plantor i mossan.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120552692</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Granhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569685</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6567686</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5068-2020 artfynd.xlsx
+++ b/artfynd/A 5068-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3630,6 +3630,276 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120618468</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Granhult, Barråsen, Näshulta, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>569642</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6567760</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120618549</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Granhult, Barråsen, Näshulta, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569691</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6567707</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Fuktig barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
